--- a/development/one_file_rosetta_output/SP116520_rosetta.xlsx
+++ b/development/one_file_rosetta_output/SP116520_rosetta.xlsx
@@ -398,14 +398,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:E195"/>
+  <dimension ref="A1:F195"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
     <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
     <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="4.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="70.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="7.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="4.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="70.711"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -426,10 +427,15 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
+          <t>N indels</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
           <t>Example n</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Indel in context</t>
         </is>
@@ -452,9 +458,12 @@
         </is>
       </c>
       <c r="D2" s="4">
-        <v>1</v>
-      </c>
-      <c r="E2" s="6" t="inlineStr">
+        <v>5</v>
+      </c>
+      <c r="E2" s="4">
+        <v>1</v>
+      </c>
+      <c r="F2" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -508,9 +517,12 @@
         </is>
       </c>
       <c r="D3" s="4">
+        <v>5</v>
+      </c>
+      <c r="E3" s="4">
         <v>2</v>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="F3" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -564,9 +576,12 @@
         </is>
       </c>
       <c r="D4" s="4">
+        <v>5</v>
+      </c>
+      <c r="E4" s="4">
         <v>3</v>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -622,7 +637,10 @@
       <c r="D5" s="4">
         <v>1</v>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="E5" s="4">
+        <v>1</v>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -676,9 +694,12 @@
         </is>
       </c>
       <c r="D6" s="4">
-        <v>1</v>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
+        <v>10</v>
+      </c>
+      <c r="E6" s="4">
+        <v>1</v>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -732,9 +753,12 @@
         </is>
       </c>
       <c r="D7" s="4">
+        <v>10</v>
+      </c>
+      <c r="E7" s="4">
         <v>2</v>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="F7" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -788,9 +812,12 @@
         </is>
       </c>
       <c r="D8" s="4">
+        <v>10</v>
+      </c>
+      <c r="E8" s="4">
         <v>3</v>
       </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="F8" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -844,9 +871,12 @@
         </is>
       </c>
       <c r="D9" s="4">
+        <v>10</v>
+      </c>
+      <c r="E9" s="4">
         <v>4</v>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="F9" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -900,9 +930,12 @@
         </is>
       </c>
       <c r="D10" s="4">
+        <v>10</v>
+      </c>
+      <c r="E10" s="4">
         <v>5</v>
       </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="F10" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -956,9 +989,12 @@
         </is>
       </c>
       <c r="D11" s="4">
-        <v>1</v>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="E11" s="4">
+        <v>1</v>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1021,7 +1057,10 @@
       <c r="D12" s="4">
         <v>2</v>
       </c>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="E12" s="4">
+        <v>2</v>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1082,9 +1121,12 @@
         </is>
       </c>
       <c r="D13" s="4">
-        <v>1</v>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="E13" s="4">
+        <v>1</v>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1145,9 +1187,12 @@
         </is>
       </c>
       <c r="D14" s="4">
+        <v>4</v>
+      </c>
+      <c r="E14" s="4">
         <v>2</v>
       </c>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="F14" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1208,9 +1253,12 @@
         </is>
       </c>
       <c r="D15" s="4">
-        <v>1</v>
-      </c>
-      <c r="E15" s="6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="E15" s="4">
+        <v>1</v>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -1238,7 +1286,10 @@
       <c r="D16" s="4">
         <v>1</v>
       </c>
-      <c r="E16" s="6" t="inlineStr">
+      <c r="E16" s="4">
+        <v>1</v>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1314,9 +1365,12 @@
         </is>
       </c>
       <c r="D17" s="4">
-        <v>1</v>
-      </c>
-      <c r="E17" s="6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="E17" s="4">
+        <v>1</v>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1400,9 +1454,12 @@
         </is>
       </c>
       <c r="D18" s="4">
-        <v>1</v>
-      </c>
-      <c r="E18" s="6" t="inlineStr">
+        <v>6</v>
+      </c>
+      <c r="E18" s="4">
+        <v>1</v>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1458,7 +1515,10 @@
       <c r="D19" s="4">
         <v>1</v>
       </c>
-      <c r="E19" s="6" t="inlineStr">
+      <c r="E19" s="4">
+        <v>1</v>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1521,7 +1581,10 @@
       <c r="D20" s="4">
         <v>1</v>
       </c>
-      <c r="E20" s="6" t="inlineStr">
+      <c r="E20" s="4">
+        <v>1</v>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1582,9 +1645,12 @@
         </is>
       </c>
       <c r="D21" s="4">
-        <v>1</v>
-      </c>
-      <c r="E21" s="6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="E21" s="4">
+        <v>1</v>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1645,9 +1711,12 @@
         </is>
       </c>
       <c r="D22" s="4">
-        <v>1</v>
-      </c>
-      <c r="E22" s="6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="E22" s="4">
+        <v>1</v>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1718,7 +1787,10 @@
       <c r="D23" s="4">
         <v>1</v>
       </c>
-      <c r="E23" s="6" t="inlineStr">
+      <c r="E23" s="4">
+        <v>1</v>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -1746,7 +1818,10 @@
       <c r="D24" s="4">
         <v>1</v>
       </c>
-      <c r="E24" s="6" t="inlineStr">
+      <c r="E24" s="4">
+        <v>1</v>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -1774,7 +1849,10 @@
       <c r="D25" s="4">
         <v>1</v>
       </c>
-      <c r="E25" s="6" t="inlineStr">
+      <c r="E25" s="4">
+        <v>1</v>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1828,9 +1906,12 @@
         </is>
       </c>
       <c r="D26" s="4">
-        <v>1</v>
-      </c>
-      <c r="E26" s="6" t="inlineStr">
+        <v>13</v>
+      </c>
+      <c r="E26" s="4">
+        <v>1</v>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1884,9 +1965,12 @@
         </is>
       </c>
       <c r="D27" s="4">
+        <v>13</v>
+      </c>
+      <c r="E27" s="4">
         <v>2</v>
       </c>
-      <c r="E27" s="6" t="inlineStr">
+      <c r="F27" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1940,9 +2024,12 @@
         </is>
       </c>
       <c r="D28" s="4">
+        <v>13</v>
+      </c>
+      <c r="E28" s="4">
         <v>3</v>
       </c>
-      <c r="E28" s="6" t="inlineStr">
+      <c r="F28" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1996,9 +2083,12 @@
         </is>
       </c>
       <c r="D29" s="4">
+        <v>13</v>
+      </c>
+      <c r="E29" s="4">
         <v>4</v>
       </c>
-      <c r="E29" s="6" t="inlineStr">
+      <c r="F29" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2052,9 +2142,12 @@
         </is>
       </c>
       <c r="D30" s="4">
+        <v>13</v>
+      </c>
+      <c r="E30" s="4">
         <v>5</v>
       </c>
-      <c r="E30" s="6" t="inlineStr">
+      <c r="F30" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2108,9 +2201,12 @@
         </is>
       </c>
       <c r="D31" s="4">
-        <v>1</v>
-      </c>
-      <c r="E31" s="6" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="E31" s="4">
+        <v>1</v>
+      </c>
+      <c r="F31" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2171,9 +2267,12 @@
         </is>
       </c>
       <c r="D32" s="4">
+        <v>4</v>
+      </c>
+      <c r="E32" s="4">
         <v>2</v>
       </c>
-      <c r="E32" s="6" t="inlineStr">
+      <c r="F32" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2234,9 +2333,12 @@
         </is>
       </c>
       <c r="D33" s="4">
+        <v>4</v>
+      </c>
+      <c r="E33" s="4">
         <v>3</v>
       </c>
-      <c r="E33" s="6" t="inlineStr">
+      <c r="F33" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2299,7 +2401,10 @@
       <c r="D34" s="4">
         <v>1</v>
       </c>
-      <c r="E34" s="6" t="inlineStr">
+      <c r="E34" s="4">
+        <v>1</v>
+      </c>
+      <c r="F34" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -2325,9 +2430,12 @@
         </is>
       </c>
       <c r="D35" s="4">
-        <v>1</v>
-      </c>
-      <c r="E35" s="6" t="inlineStr">
+        <v>6</v>
+      </c>
+      <c r="E35" s="4">
+        <v>1</v>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2390,7 +2498,10 @@
       <c r="D36" s="4">
         <v>1</v>
       </c>
-      <c r="E36" s="6" t="inlineStr">
+      <c r="E36" s="4">
+        <v>1</v>
+      </c>
+      <c r="F36" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2459,9 +2570,12 @@
         </is>
       </c>
       <c r="D37" s="4">
-        <v>1</v>
-      </c>
-      <c r="E37" s="6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="E37" s="4">
+        <v>1</v>
+      </c>
+      <c r="F37" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2532,7 +2646,10 @@
       <c r="D38" s="4">
         <v>1</v>
       </c>
-      <c r="E38" s="6" t="inlineStr">
+      <c r="E38" s="4">
+        <v>1</v>
+      </c>
+      <c r="F38" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2610,7 +2727,10 @@
       <c r="D39" s="4">
         <v>1</v>
       </c>
-      <c r="E39" s="6" t="inlineStr">
+      <c r="E39" s="4">
+        <v>1</v>
+      </c>
+      <c r="F39" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -2638,7 +2758,10 @@
       <c r="D40" s="4">
         <v>1</v>
       </c>
-      <c r="E40" s="6" t="inlineStr">
+      <c r="E40" s="4">
+        <v>1</v>
+      </c>
+      <c r="F40" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2729,9 +2852,12 @@
         </is>
       </c>
       <c r="D41" s="4">
-        <v>1</v>
-      </c>
-      <c r="E41" s="6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="E41" s="4">
+        <v>1</v>
+      </c>
+      <c r="F41" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -2757,9 +2883,12 @@
         </is>
       </c>
       <c r="D42" s="4">
-        <v>1</v>
-      </c>
-      <c r="E42" s="6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="E42" s="4">
+        <v>1</v>
+      </c>
+      <c r="F42" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2815,7 +2944,10 @@
       <c r="D43" s="4">
         <v>1</v>
       </c>
-      <c r="E43" s="6" t="inlineStr">
+      <c r="E43" s="4">
+        <v>1</v>
+      </c>
+      <c r="F43" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -2843,7 +2975,10 @@
       <c r="D44" s="4">
         <v>1</v>
       </c>
-      <c r="E44" s="6" t="inlineStr">
+      <c r="E44" s="4">
+        <v>1</v>
+      </c>
+      <c r="F44" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -2871,7 +3006,10 @@
       <c r="D45" s="4">
         <v>1</v>
       </c>
-      <c r="E45" s="6" t="inlineStr">
+      <c r="E45" s="4">
+        <v>1</v>
+      </c>
+      <c r="F45" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2940,9 +3078,12 @@
         </is>
       </c>
       <c r="D46" s="4">
-        <v>1</v>
-      </c>
-      <c r="E46" s="6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="E46" s="4">
+        <v>1</v>
+      </c>
+      <c r="F46" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -2968,9 +3109,12 @@
         </is>
       </c>
       <c r="D47" s="4">
-        <v>1</v>
-      </c>
-      <c r="E47" s="6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="E47" s="4">
+        <v>1</v>
+      </c>
+      <c r="F47" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3048,7 +3192,10 @@
       <c r="D48" s="4">
         <v>1</v>
       </c>
-      <c r="E48" s="6" t="inlineStr">
+      <c r="E48" s="4">
+        <v>1</v>
+      </c>
+      <c r="F48" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3126,7 +3273,10 @@
       <c r="D49" s="4">
         <v>1</v>
       </c>
-      <c r="E49" s="6" t="inlineStr">
+      <c r="E49" s="4">
+        <v>1</v>
+      </c>
+      <c r="F49" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -3152,9 +3302,12 @@
         </is>
       </c>
       <c r="D50" s="4">
-        <v>1</v>
-      </c>
-      <c r="E50" s="6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="E50" s="4">
+        <v>1</v>
+      </c>
+      <c r="F50" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3238,9 +3391,12 @@
         </is>
       </c>
       <c r="D51" s="4">
-        <v>1</v>
-      </c>
-      <c r="E51" s="6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="E51" s="4">
+        <v>1</v>
+      </c>
+      <c r="F51" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3326,7 +3482,10 @@
       <c r="D52" s="4">
         <v>1</v>
       </c>
-      <c r="E52" s="6" t="inlineStr">
+      <c r="E52" s="4">
+        <v>1</v>
+      </c>
+      <c r="F52" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3417,9 +3576,12 @@
         </is>
       </c>
       <c r="D53" s="4">
-        <v>1</v>
-      </c>
-      <c r="E53" s="6" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="E53" s="4">
+        <v>1</v>
+      </c>
+      <c r="F53" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3510,9 +3672,12 @@
         </is>
       </c>
       <c r="D54" s="4">
+        <v>3</v>
+      </c>
+      <c r="E54" s="4">
         <v>2</v>
       </c>
-      <c r="E54" s="6" t="inlineStr">
+      <c r="F54" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3603,9 +3768,12 @@
         </is>
       </c>
       <c r="D55" s="4">
-        <v>1</v>
-      </c>
-      <c r="E55" s="6" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="E55" s="4">
+        <v>1</v>
+      </c>
+      <c r="F55" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -3633,7 +3801,10 @@
       <c r="D56" s="4">
         <v>1</v>
       </c>
-      <c r="E56" s="6" t="inlineStr">
+      <c r="E56" s="4">
+        <v>1</v>
+      </c>
+      <c r="F56" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -3661,7 +3832,10 @@
       <c r="D57" s="4">
         <v>1</v>
       </c>
-      <c r="E57" s="6" t="inlineStr">
+      <c r="E57" s="4">
+        <v>1</v>
+      </c>
+      <c r="F57" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -3687,9 +3861,12 @@
         </is>
       </c>
       <c r="D58" s="4">
-        <v>1</v>
-      </c>
-      <c r="E58" s="6" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="E58" s="4">
+        <v>1</v>
+      </c>
+      <c r="F58" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3797,7 +3974,10 @@
       <c r="D59" s="4">
         <v>1</v>
       </c>
-      <c r="E59" s="6" t="inlineStr">
+      <c r="E59" s="4">
+        <v>1</v>
+      </c>
+      <c r="F59" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -3823,9 +4003,12 @@
         </is>
       </c>
       <c r="D60" s="4">
-        <v>1</v>
-      </c>
-      <c r="E60" s="6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="E60" s="4">
+        <v>1</v>
+      </c>
+      <c r="F60" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3941,7 +4124,10 @@
       <c r="D61" s="4">
         <v>2</v>
       </c>
-      <c r="E61" s="6" t="inlineStr">
+      <c r="E61" s="4">
+        <v>2</v>
+      </c>
+      <c r="F61" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4057,7 +4243,10 @@
       <c r="D62" s="4">
         <v>1</v>
       </c>
-      <c r="E62" s="6" t="inlineStr">
+      <c r="E62" s="4">
+        <v>1</v>
+      </c>
+      <c r="F62" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -4085,7 +4274,10 @@
       <c r="D63" s="4">
         <v>1</v>
       </c>
-      <c r="E63" s="6" t="inlineStr">
+      <c r="E63" s="4">
+        <v>1</v>
+      </c>
+      <c r="F63" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4139,9 +4331,12 @@
         </is>
       </c>
       <c r="D64" s="4">
-        <v>1</v>
-      </c>
-      <c r="E64" s="6" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="E64" s="4">
+        <v>1</v>
+      </c>
+      <c r="F64" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -4169,7 +4364,10 @@
       <c r="D65" s="4">
         <v>1</v>
       </c>
-      <c r="E65" s="6" t="inlineStr">
+      <c r="E65" s="4">
+        <v>1</v>
+      </c>
+      <c r="F65" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -4195,9 +4393,12 @@
         </is>
       </c>
       <c r="D66" s="4">
-        <v>1</v>
-      </c>
-      <c r="E66" s="6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="E66" s="4">
+        <v>1</v>
+      </c>
+      <c r="F66" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4258,9 +4459,12 @@
         </is>
       </c>
       <c r="D67" s="4">
-        <v>1</v>
-      </c>
-      <c r="E67" s="6" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="E67" s="4">
+        <v>1</v>
+      </c>
+      <c r="F67" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4331,7 +4535,10 @@
       <c r="D68" s="4">
         <v>1</v>
       </c>
-      <c r="E68" s="6" t="inlineStr">
+      <c r="E68" s="4">
+        <v>1</v>
+      </c>
+      <c r="F68" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -4359,7 +4566,10 @@
       <c r="D69" s="4">
         <v>1</v>
       </c>
-      <c r="E69" s="6" t="inlineStr">
+      <c r="E69" s="4">
+        <v>1</v>
+      </c>
+      <c r="F69" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -4385,9 +4595,12 @@
         </is>
       </c>
       <c r="D70" s="4">
-        <v>1</v>
-      </c>
-      <c r="E70" s="6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="E70" s="4">
+        <v>1</v>
+      </c>
+      <c r="F70" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4463,9 +4676,12 @@
         </is>
       </c>
       <c r="D71" s="4">
-        <v>1</v>
-      </c>
-      <c r="E71" s="6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="E71" s="4">
+        <v>1</v>
+      </c>
+      <c r="F71" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4543,7 +4759,10 @@
       <c r="D72" s="4">
         <v>2</v>
       </c>
-      <c r="E72" s="6" t="inlineStr">
+      <c r="E72" s="4">
+        <v>2</v>
+      </c>
+      <c r="F72" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4621,7 +4840,10 @@
       <c r="D73" s="4">
         <v>1</v>
       </c>
-      <c r="E73" s="6" t="inlineStr">
+      <c r="E73" s="4">
+        <v>1</v>
+      </c>
+      <c r="F73" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4705,9 +4927,12 @@
         </is>
       </c>
       <c r="D74" s="4">
-        <v>1</v>
-      </c>
-      <c r="E74" s="6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="E74" s="4">
+        <v>1</v>
+      </c>
+      <c r="F74" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4800,7 +5025,10 @@
       <c r="D75" s="4">
         <v>2</v>
       </c>
-      <c r="E75" s="6" t="inlineStr">
+      <c r="E75" s="4">
+        <v>2</v>
+      </c>
+      <c r="F75" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4891,9 +5119,12 @@
         </is>
       </c>
       <c r="D76" s="4">
-        <v>1</v>
-      </c>
-      <c r="E76" s="6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="E76" s="4">
+        <v>1</v>
+      </c>
+      <c r="F76" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4994,7 +5225,10 @@
       <c r="D77" s="4">
         <v>2</v>
       </c>
-      <c r="E77" s="6" t="inlineStr">
+      <c r="E77" s="4">
+        <v>2</v>
+      </c>
+      <c r="F77" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5095,7 +5329,10 @@
       <c r="D78" s="4">
         <v>1</v>
       </c>
-      <c r="E78" s="6" t="inlineStr">
+      <c r="E78" s="4">
+        <v>1</v>
+      </c>
+      <c r="F78" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5196,7 +5433,10 @@
       <c r="D79" s="4">
         <v>1</v>
       </c>
-      <c r="E79" s="6" t="inlineStr">
+      <c r="E79" s="4">
+        <v>1</v>
+      </c>
+      <c r="F79" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5304,7 +5544,10 @@
       <c r="D80" s="4">
         <v>1</v>
       </c>
-      <c r="E80" s="6" t="inlineStr">
+      <c r="E80" s="4">
+        <v>1</v>
+      </c>
+      <c r="F80" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5418,9 +5661,12 @@
         </is>
       </c>
       <c r="D81" s="4">
-        <v>1</v>
-      </c>
-      <c r="E81" s="6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="E81" s="4">
+        <v>1</v>
+      </c>
+      <c r="F81" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5476,7 +5722,10 @@
       <c r="D82" s="4">
         <v>1</v>
       </c>
-      <c r="E82" s="6" t="inlineStr">
+      <c r="E82" s="4">
+        <v>1</v>
+      </c>
+      <c r="F82" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5532,7 +5781,10 @@
       <c r="D83" s="4">
         <v>1</v>
       </c>
-      <c r="E83" s="6" t="inlineStr">
+      <c r="E83" s="4">
+        <v>1</v>
+      </c>
+      <c r="F83" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5595,7 +5847,10 @@
       <c r="D84" s="4">
         <v>1</v>
       </c>
-      <c r="E84" s="6" t="inlineStr">
+      <c r="E84" s="4">
+        <v>1</v>
+      </c>
+      <c r="F84" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -5623,7 +5878,10 @@
       <c r="D85" s="4">
         <v>1</v>
       </c>
-      <c r="E85" s="6" t="inlineStr">
+      <c r="E85" s="4">
+        <v>1</v>
+      </c>
+      <c r="F85" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -5651,7 +5909,10 @@
       <c r="D86" s="4">
         <v>1</v>
       </c>
-      <c r="E86" s="6" t="inlineStr">
+      <c r="E86" s="4">
+        <v>1</v>
+      </c>
+      <c r="F86" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5720,9 +5981,12 @@
         </is>
       </c>
       <c r="D87" s="4">
-        <v>1</v>
-      </c>
-      <c r="E87" s="6" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="E87" s="4">
+        <v>1</v>
+      </c>
+      <c r="F87" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5791,9 +6055,12 @@
         </is>
       </c>
       <c r="D88" s="4">
+        <v>3</v>
+      </c>
+      <c r="E88" s="4">
         <v>2</v>
       </c>
-      <c r="E88" s="6" t="inlineStr">
+      <c r="F88" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5862,9 +6129,12 @@
         </is>
       </c>
       <c r="D89" s="4">
-        <v>1</v>
-      </c>
-      <c r="E89" s="6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="E89" s="4">
+        <v>1</v>
+      </c>
+      <c r="F89" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -5890,9 +6160,12 @@
         </is>
       </c>
       <c r="D90" s="4">
-        <v>1</v>
-      </c>
-      <c r="E90" s="6" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="E90" s="4">
+        <v>1</v>
+      </c>
+      <c r="F90" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5976,9 +6249,12 @@
         </is>
       </c>
       <c r="D91" s="4">
+        <v>3</v>
+      </c>
+      <c r="E91" s="4">
         <v>2</v>
       </c>
-      <c r="E91" s="6" t="inlineStr">
+      <c r="F91" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6064,7 +6340,10 @@
       <c r="D92" s="4">
         <v>3</v>
       </c>
-      <c r="E92" s="6" t="inlineStr">
+      <c r="E92" s="4">
+        <v>3</v>
+      </c>
+      <c r="F92" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6148,9 +6427,12 @@
         </is>
       </c>
       <c r="D93" s="4">
-        <v>1</v>
-      </c>
-      <c r="E93" s="6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="E93" s="4">
+        <v>1</v>
+      </c>
+      <c r="F93" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6234,9 +6516,12 @@
         </is>
       </c>
       <c r="D94" s="4">
-        <v>1</v>
-      </c>
-      <c r="E94" s="6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="E94" s="4">
+        <v>1</v>
+      </c>
+      <c r="F94" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6322,7 +6607,10 @@
       <c r="D95" s="4">
         <v>2</v>
       </c>
-      <c r="E95" s="6" t="inlineStr">
+      <c r="E95" s="4">
+        <v>2</v>
+      </c>
+      <c r="F95" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6406,9 +6694,12 @@
         </is>
       </c>
       <c r="D96" s="4">
-        <v>1</v>
-      </c>
-      <c r="E96" s="6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="E96" s="4">
+        <v>1</v>
+      </c>
+      <c r="F96" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6499,9 +6790,12 @@
         </is>
       </c>
       <c r="D97" s="4">
-        <v>1</v>
-      </c>
-      <c r="E97" s="6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="E97" s="4">
+        <v>1</v>
+      </c>
+      <c r="F97" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6594,7 +6888,10 @@
       <c r="D98" s="4">
         <v>2</v>
       </c>
-      <c r="E98" s="6" t="inlineStr">
+      <c r="E98" s="4">
+        <v>2</v>
+      </c>
+      <c r="F98" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6687,7 +6984,10 @@
       <c r="D99" s="4">
         <v>1</v>
       </c>
-      <c r="E99" s="6" t="inlineStr">
+      <c r="E99" s="4">
+        <v>1</v>
+      </c>
+      <c r="F99" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6743,7 +7043,10 @@
       <c r="D100" s="4">
         <v>1</v>
       </c>
-      <c r="E100" s="6" t="inlineStr">
+      <c r="E100" s="4">
+        <v>1</v>
+      </c>
+      <c r="F100" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -6771,7 +7074,10 @@
       <c r="D101" s="4">
         <v>1</v>
       </c>
-      <c r="E101" s="6" t="inlineStr">
+      <c r="E101" s="4">
+        <v>1</v>
+      </c>
+      <c r="F101" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6834,7 +7140,10 @@
       <c r="D102" s="4">
         <v>1</v>
       </c>
-      <c r="E102" s="6" t="inlineStr">
+      <c r="E102" s="4">
+        <v>1</v>
+      </c>
+      <c r="F102" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6897,7 +7206,10 @@
       <c r="D103" s="4">
         <v>1</v>
       </c>
-      <c r="E103" s="6" t="inlineStr">
+      <c r="E103" s="4">
+        <v>1</v>
+      </c>
+      <c r="F103" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6975,7 +7287,10 @@
       <c r="D104" s="4">
         <v>1</v>
       </c>
-      <c r="E104" s="6" t="inlineStr">
+      <c r="E104" s="4">
+        <v>1</v>
+      </c>
+      <c r="F104" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7031,7 +7346,10 @@
       <c r="D105" s="4">
         <v>1</v>
       </c>
-      <c r="E105" s="6" t="inlineStr">
+      <c r="E105" s="4">
+        <v>1</v>
+      </c>
+      <c r="F105" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7094,7 +7412,10 @@
       <c r="D106" s="4">
         <v>1</v>
       </c>
-      <c r="E106" s="6" t="inlineStr">
+      <c r="E106" s="4">
+        <v>1</v>
+      </c>
+      <c r="F106" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -7122,7 +7443,10 @@
       <c r="D107" s="4">
         <v>1</v>
       </c>
-      <c r="E107" s="6" t="inlineStr">
+      <c r="E107" s="4">
+        <v>1</v>
+      </c>
+      <c r="F107" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7191,9 +7515,12 @@
         </is>
       </c>
       <c r="D108" s="4">
-        <v>1</v>
-      </c>
-      <c r="E108" s="6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="E108" s="4">
+        <v>1</v>
+      </c>
+      <c r="F108" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7286,7 +7613,10 @@
       <c r="D109" s="4">
         <v>2</v>
       </c>
-      <c r="E109" s="6" t="inlineStr">
+      <c r="E109" s="4">
+        <v>2</v>
+      </c>
+      <c r="F109" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7379,7 +7709,10 @@
       <c r="D110" s="4">
         <v>1</v>
       </c>
-      <c r="E110" s="6" t="inlineStr">
+      <c r="E110" s="4">
+        <v>1</v>
+      </c>
+      <c r="F110" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7472,7 +7805,10 @@
       <c r="D111" s="4">
         <v>1</v>
       </c>
-      <c r="E111" s="6" t="inlineStr">
+      <c r="E111" s="4">
+        <v>1</v>
+      </c>
+      <c r="F111" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -7498,9 +7834,12 @@
         </is>
       </c>
       <c r="D112" s="4">
-        <v>1</v>
-      </c>
-      <c r="E112" s="6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="E112" s="4">
+        <v>1</v>
+      </c>
+      <c r="F112" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -7528,7 +7867,10 @@
       <c r="D113" s="4">
         <v>1</v>
       </c>
-      <c r="E113" s="6" t="inlineStr">
+      <c r="E113" s="4">
+        <v>1</v>
+      </c>
+      <c r="F113" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -7556,7 +7898,10 @@
       <c r="D114" s="4">
         <v>1</v>
       </c>
-      <c r="E114" s="6" t="inlineStr">
+      <c r="E114" s="4">
+        <v>1</v>
+      </c>
+      <c r="F114" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -7584,7 +7929,10 @@
       <c r="D115" s="4">
         <v>1</v>
       </c>
-      <c r="E115" s="6" t="inlineStr">
+      <c r="E115" s="4">
+        <v>1</v>
+      </c>
+      <c r="F115" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -7610,9 +7958,12 @@
         </is>
       </c>
       <c r="D116" s="4">
-        <v>1</v>
-      </c>
-      <c r="E116" s="6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="E116" s="4">
+        <v>1</v>
+      </c>
+      <c r="F116" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7726,9 +8077,12 @@
         </is>
       </c>
       <c r="D117" s="4">
-        <v>1</v>
-      </c>
-      <c r="E117" s="6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="E117" s="4">
+        <v>1</v>
+      </c>
+      <c r="F117" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7844,7 +8198,10 @@
       <c r="D118" s="4">
         <v>2</v>
       </c>
-      <c r="E118" s="6" t="inlineStr">
+      <c r="E118" s="4">
+        <v>2</v>
+      </c>
+      <c r="F118" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7960,7 +8317,10 @@
       <c r="D119" s="4">
         <v>1</v>
       </c>
-      <c r="E119" s="6" t="inlineStr">
+      <c r="E119" s="4">
+        <v>1</v>
+      </c>
+      <c r="F119" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8083,7 +8443,10 @@
       <c r="D120" s="4">
         <v>1</v>
       </c>
-      <c r="E120" s="6" t="inlineStr">
+      <c r="E120" s="4">
+        <v>1</v>
+      </c>
+      <c r="F120" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -8111,7 +8474,10 @@
       <c r="D121" s="4">
         <v>1</v>
       </c>
-      <c r="E121" s="6" t="inlineStr">
+      <c r="E121" s="4">
+        <v>1</v>
+      </c>
+      <c r="F121" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8174,7 +8540,10 @@
       <c r="D122" s="4">
         <v>1</v>
       </c>
-      <c r="E122" s="6" t="inlineStr">
+      <c r="E122" s="4">
+        <v>1</v>
+      </c>
+      <c r="F122" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8275,7 +8644,10 @@
       <c r="D123" s="4">
         <v>1</v>
       </c>
-      <c r="E123" s="6" t="inlineStr">
+      <c r="E123" s="4">
+        <v>1</v>
+      </c>
+      <c r="F123" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8383,7 +8755,10 @@
       <c r="D124" s="4">
         <v>1</v>
       </c>
-      <c r="E124" s="6" t="inlineStr">
+      <c r="E124" s="4">
+        <v>1</v>
+      </c>
+      <c r="F124" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8499,7 +8874,10 @@
       <c r="D125" s="4">
         <v>1</v>
       </c>
-      <c r="E125" s="6" t="inlineStr">
+      <c r="E125" s="4">
+        <v>1</v>
+      </c>
+      <c r="F125" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8622,7 +9000,10 @@
       <c r="D126" s="4">
         <v>1</v>
       </c>
-      <c r="E126" s="6" t="inlineStr">
+      <c r="E126" s="4">
+        <v>1</v>
+      </c>
+      <c r="F126" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8745,7 +9126,10 @@
       <c r="D127" s="4">
         <v>1</v>
       </c>
-      <c r="E127" s="6" t="inlineStr">
+      <c r="E127" s="4">
+        <v>1</v>
+      </c>
+      <c r="F127" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -8773,7 +9157,10 @@
       <c r="D128" s="4">
         <v>1</v>
       </c>
-      <c r="E128" s="6" t="inlineStr">
+      <c r="E128" s="4">
+        <v>1</v>
+      </c>
+      <c r="F128" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -8799,9 +9186,12 @@
         </is>
       </c>
       <c r="D129" s="4">
-        <v>1</v>
-      </c>
-      <c r="E129" s="6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="E129" s="4">
+        <v>1</v>
+      </c>
+      <c r="F129" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8902,7 +9292,10 @@
       <c r="D130" s="4">
         <v>2</v>
       </c>
-      <c r="E130" s="6" t="inlineStr">
+      <c r="E130" s="4">
+        <v>2</v>
+      </c>
+      <c r="F130" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9003,7 +9396,10 @@
       <c r="D131" s="4">
         <v>1</v>
       </c>
-      <c r="E131" s="6" t="inlineStr">
+      <c r="E131" s="4">
+        <v>1</v>
+      </c>
+      <c r="F131" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -9029,9 +9425,12 @@
         </is>
       </c>
       <c r="D132" s="4">
-        <v>1</v>
-      </c>
-      <c r="E132" s="6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="E132" s="4">
+        <v>1</v>
+      </c>
+      <c r="F132" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9139,7 +9538,10 @@
       <c r="D133" s="4">
         <v>2</v>
       </c>
-      <c r="E133" s="6" t="inlineStr">
+      <c r="E133" s="4">
+        <v>2</v>
+      </c>
+      <c r="F133" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9247,7 +9649,10 @@
       <c r="D134" s="4">
         <v>1</v>
       </c>
-      <c r="E134" s="6" t="inlineStr">
+      <c r="E134" s="4">
+        <v>1</v>
+      </c>
+      <c r="F134" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9363,7 +9768,10 @@
       <c r="D135" s="4">
         <v>1</v>
       </c>
-      <c r="E135" s="6" t="inlineStr">
+      <c r="E135" s="4">
+        <v>1</v>
+      </c>
+      <c r="F135" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9419,7 +9827,10 @@
       <c r="D136" s="4">
         <v>1</v>
       </c>
-      <c r="E136" s="6" t="inlineStr">
+      <c r="E136" s="4">
+        <v>1</v>
+      </c>
+      <c r="F136" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9473,9 +9884,12 @@
         </is>
       </c>
       <c r="D137" s="4">
-        <v>1</v>
-      </c>
-      <c r="E137" s="6" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="E137" s="4">
+        <v>1</v>
+      </c>
+      <c r="F137" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9529,9 +9943,12 @@
         </is>
       </c>
       <c r="D138" s="4">
+        <v>3</v>
+      </c>
+      <c r="E138" s="4">
         <v>2</v>
       </c>
-      <c r="E138" s="6" t="inlineStr">
+      <c r="F138" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9587,7 +10004,10 @@
       <c r="D139" s="4">
         <v>3</v>
       </c>
-      <c r="E139" s="6" t="inlineStr">
+      <c r="E139" s="4">
+        <v>3</v>
+      </c>
+      <c r="F139" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9643,7 +10063,10 @@
       <c r="D140" s="4">
         <v>1</v>
       </c>
-      <c r="E140" s="6" t="inlineStr">
+      <c r="E140" s="4">
+        <v>1</v>
+      </c>
+      <c r="F140" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9697,9 +10120,12 @@
         </is>
       </c>
       <c r="D141" s="4">
-        <v>1</v>
-      </c>
-      <c r="E141" s="6" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="E141" s="4">
+        <v>1</v>
+      </c>
+      <c r="F141" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9753,9 +10179,12 @@
         </is>
       </c>
       <c r="D142" s="4">
+        <v>4</v>
+      </c>
+      <c r="E142" s="4">
         <v>2</v>
       </c>
-      <c r="E142" s="6" t="inlineStr">
+      <c r="F142" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9809,9 +10238,12 @@
         </is>
       </c>
       <c r="D143" s="4">
+        <v>4</v>
+      </c>
+      <c r="E143" s="4">
         <v>3</v>
       </c>
-      <c r="E143" s="6" t="inlineStr">
+      <c r="F143" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9867,7 +10299,10 @@
       <c r="D144" s="4">
         <v>1</v>
       </c>
-      <c r="E144" s="6" t="inlineStr">
+      <c r="E144" s="4">
+        <v>1</v>
+      </c>
+      <c r="F144" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9943,9 +10378,12 @@
         </is>
       </c>
       <c r="D145" s="4">
-        <v>1</v>
-      </c>
-      <c r="E145" s="6" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="E145" s="4">
+        <v>1</v>
+      </c>
+      <c r="F145" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10006,9 +10444,12 @@
         </is>
       </c>
       <c r="D146" s="4">
+        <v>3</v>
+      </c>
+      <c r="E146" s="4">
         <v>2</v>
       </c>
-      <c r="E146" s="6" t="inlineStr">
+      <c r="F146" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10071,7 +10512,10 @@
       <c r="D147" s="4">
         <v>3</v>
       </c>
-      <c r="E147" s="6" t="inlineStr">
+      <c r="E147" s="4">
+        <v>3</v>
+      </c>
+      <c r="F147" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10134,7 +10578,10 @@
       <c r="D148" s="4">
         <v>1</v>
       </c>
-      <c r="E148" s="6" t="inlineStr">
+      <c r="E148" s="4">
+        <v>1</v>
+      </c>
+      <c r="F148" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10225,9 +10672,12 @@
         </is>
       </c>
       <c r="D149" s="4">
-        <v>1</v>
-      </c>
-      <c r="E149" s="6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="E149" s="4">
+        <v>1</v>
+      </c>
+      <c r="F149" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10290,7 +10740,10 @@
       <c r="D150" s="4">
         <v>2</v>
       </c>
-      <c r="E150" s="6" t="inlineStr">
+      <c r="E150" s="4">
+        <v>2</v>
+      </c>
+      <c r="F150" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10353,7 +10806,10 @@
       <c r="D151" s="4">
         <v>1</v>
       </c>
-      <c r="E151" s="6" t="inlineStr">
+      <c r="E151" s="4">
+        <v>1</v>
+      </c>
+      <c r="F151" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10424,7 +10880,10 @@
       <c r="D152" s="4">
         <v>1</v>
       </c>
-      <c r="E152" s="6" t="inlineStr">
+      <c r="E152" s="4">
+        <v>1</v>
+      </c>
+      <c r="F152" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10540,7 +10999,10 @@
       <c r="D153" s="4">
         <v>1</v>
       </c>
-      <c r="E153" s="6" t="inlineStr">
+      <c r="E153" s="4">
+        <v>1</v>
+      </c>
+      <c r="F153" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10601,9 +11063,12 @@
         </is>
       </c>
       <c r="D154" s="4">
-        <v>1</v>
-      </c>
-      <c r="E154" s="6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="E154" s="4">
+        <v>1</v>
+      </c>
+      <c r="F154" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10674,7 +11139,10 @@
       <c r="D155" s="4">
         <v>2</v>
       </c>
-      <c r="E155" s="6" t="inlineStr">
+      <c r="E155" s="4">
+        <v>2</v>
+      </c>
+      <c r="F155" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10745,7 +11213,10 @@
       <c r="D156" s="4">
         <v>1</v>
       </c>
-      <c r="E156" s="6" t="inlineStr">
+      <c r="E156" s="4">
+        <v>1</v>
+      </c>
+      <c r="F156" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10821,9 +11292,12 @@
         </is>
       </c>
       <c r="D157" s="4">
-        <v>1</v>
-      </c>
-      <c r="E157" s="6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="E157" s="4">
+        <v>1</v>
+      </c>
+      <c r="F157" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10886,7 +11360,10 @@
       <c r="D158" s="4">
         <v>2</v>
       </c>
-      <c r="E158" s="6" t="inlineStr">
+      <c r="E158" s="4">
+        <v>2</v>
+      </c>
+      <c r="F158" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10949,7 +11426,10 @@
       <c r="D159" s="4">
         <v>1</v>
       </c>
-      <c r="E159" s="6" t="inlineStr">
+      <c r="E159" s="4">
+        <v>1</v>
+      </c>
+      <c r="F159" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11010,9 +11490,12 @@
         </is>
       </c>
       <c r="D160" s="4">
-        <v>1</v>
-      </c>
-      <c r="E160" s="6" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="E160" s="4">
+        <v>1</v>
+      </c>
+      <c r="F160" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11073,9 +11556,12 @@
         </is>
       </c>
       <c r="D161" s="4">
+        <v>3</v>
+      </c>
+      <c r="E161" s="4">
         <v>2</v>
       </c>
-      <c r="E161" s="6" t="inlineStr">
+      <c r="F161" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11138,7 +11624,10 @@
       <c r="D162" s="4">
         <v>3</v>
       </c>
-      <c r="E162" s="6" t="inlineStr">
+      <c r="E162" s="4">
+        <v>3</v>
+      </c>
+      <c r="F162" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11199,9 +11688,12 @@
         </is>
       </c>
       <c r="D163" s="4">
-        <v>1</v>
-      </c>
-      <c r="E163" s="6" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="E163" s="4">
+        <v>1</v>
+      </c>
+      <c r="F163" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11271,9 +11763,12 @@
         </is>
       </c>
       <c r="D164" s="4">
+        <v>3</v>
+      </c>
+      <c r="E164" s="4">
         <v>2</v>
       </c>
-      <c r="E164" s="6" t="inlineStr">
+      <c r="F164" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11345,7 +11840,10 @@
       <c r="D165" s="4">
         <v>3</v>
       </c>
-      <c r="E165" s="6" t="inlineStr">
+      <c r="E165" s="4">
+        <v>3</v>
+      </c>
+      <c r="F165" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11415,9 +11913,12 @@
         </is>
       </c>
       <c r="D166" s="4">
-        <v>1</v>
-      </c>
-      <c r="E166" s="6" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="E166" s="4">
+        <v>1</v>
+      </c>
+      <c r="F166" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11487,9 +11988,12 @@
         </is>
       </c>
       <c r="D167" s="4">
+        <v>3</v>
+      </c>
+      <c r="E167" s="4">
         <v>2</v>
       </c>
-      <c r="E167" s="6" t="inlineStr">
+      <c r="F167" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11561,7 +12065,10 @@
       <c r="D168" s="4">
         <v>3</v>
       </c>
-      <c r="E168" s="6" t="inlineStr">
+      <c r="E168" s="4">
+        <v>3</v>
+      </c>
+      <c r="F168" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11631,9 +12138,12 @@
         </is>
       </c>
       <c r="D169" s="4">
-        <v>1</v>
-      </c>
-      <c r="E169" s="6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="E169" s="4">
+        <v>1</v>
+      </c>
+      <c r="F169" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11705,7 +12215,10 @@
       <c r="D170" s="4">
         <v>2</v>
       </c>
-      <c r="E170" s="6" t="inlineStr">
+      <c r="E170" s="4">
+        <v>2</v>
+      </c>
+      <c r="F170" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11777,7 +12290,10 @@
       <c r="D171" s="4">
         <v>1</v>
       </c>
-      <c r="E171" s="6" t="inlineStr">
+      <c r="E171" s="4">
+        <v>1</v>
+      </c>
+      <c r="F171" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11847,9 +12363,12 @@
         </is>
       </c>
       <c r="D172" s="4">
-        <v>1</v>
-      </c>
-      <c r="E172" s="6" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="E172" s="4">
+        <v>1</v>
+      </c>
+      <c r="F172" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11919,9 +12438,12 @@
         </is>
       </c>
       <c r="D173" s="4">
+        <v>3</v>
+      </c>
+      <c r="E173" s="4">
         <v>2</v>
       </c>
-      <c r="E173" s="6" t="inlineStr">
+      <c r="F173" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11993,7 +12515,10 @@
       <c r="D174" s="4">
         <v>3</v>
       </c>
-      <c r="E174" s="6" t="inlineStr">
+      <c r="E174" s="4">
+        <v>3</v>
+      </c>
+      <c r="F174" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12065,7 +12590,10 @@
       <c r="D175" s="4">
         <v>1</v>
       </c>
-      <c r="E175" s="6" t="inlineStr">
+      <c r="E175" s="4">
+        <v>1</v>
+      </c>
+      <c r="F175" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12137,7 +12665,10 @@
       <c r="D176" s="4">
         <v>1</v>
       </c>
-      <c r="E176" s="6" t="inlineStr">
+      <c r="E176" s="4">
+        <v>1</v>
+      </c>
+      <c r="F176" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12209,7 +12740,10 @@
       <c r="D177" s="4">
         <v>1</v>
       </c>
-      <c r="E177" s="6" t="inlineStr">
+      <c r="E177" s="4">
+        <v>1</v>
+      </c>
+      <c r="F177" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12279,9 +12813,12 @@
         </is>
       </c>
       <c r="D178" s="4">
-        <v>1</v>
-      </c>
-      <c r="E178" s="6" t="inlineStr">
+        <v>8</v>
+      </c>
+      <c r="E178" s="4">
+        <v>1</v>
+      </c>
+      <c r="F178" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12351,9 +12888,12 @@
         </is>
       </c>
       <c r="D179" s="4">
+        <v>8</v>
+      </c>
+      <c r="E179" s="4">
         <v>2</v>
       </c>
-      <c r="E179" s="6" t="inlineStr">
+      <c r="F179" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12423,9 +12963,12 @@
         </is>
       </c>
       <c r="D180" s="4">
+        <v>8</v>
+      </c>
+      <c r="E180" s="4">
         <v>3</v>
       </c>
-      <c r="E180" s="6" t="inlineStr">
+      <c r="F180" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12495,9 +13038,12 @@
         </is>
       </c>
       <c r="D181" s="4">
+        <v>8</v>
+      </c>
+      <c r="E181" s="4">
         <v>4</v>
       </c>
-      <c r="E181" s="6" t="inlineStr">
+      <c r="F181" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12567,9 +13113,12 @@
         </is>
       </c>
       <c r="D182" s="4">
+        <v>8</v>
+      </c>
+      <c r="E182" s="4">
         <v>5</v>
       </c>
-      <c r="E182" s="6" t="inlineStr">
+      <c r="F182" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12639,9 +13188,12 @@
         </is>
       </c>
       <c r="D183" s="4">
+        <v>8</v>
+      </c>
+      <c r="E183" s="4">
         <v>6</v>
       </c>
-      <c r="E183" s="6" t="inlineStr">
+      <c r="F183" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12711,9 +13263,12 @@
         </is>
       </c>
       <c r="D184" s="4">
+        <v>8</v>
+      </c>
+      <c r="E184" s="4">
         <v>7</v>
       </c>
-      <c r="E184" s="6" t="inlineStr">
+      <c r="F184" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12785,7 +13340,10 @@
       <c r="D185" s="4">
         <v>8</v>
       </c>
-      <c r="E185" s="6" t="inlineStr">
+      <c r="E185" s="4">
+        <v>8</v>
+      </c>
+      <c r="F185" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12855,9 +13413,12 @@
         </is>
       </c>
       <c r="D186" s="4">
-        <v>1</v>
-      </c>
-      <c r="E186" s="6" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="E186" s="4">
+        <v>1</v>
+      </c>
+      <c r="F186" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12927,9 +13488,12 @@
         </is>
       </c>
       <c r="D187" s="4">
+        <v>4</v>
+      </c>
+      <c r="E187" s="4">
         <v>2</v>
       </c>
-      <c r="E187" s="6" t="inlineStr">
+      <c r="F187" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12999,9 +13563,12 @@
         </is>
       </c>
       <c r="D188" s="4">
+        <v>4</v>
+      </c>
+      <c r="E188" s="4">
         <v>3</v>
       </c>
-      <c r="E188" s="6" t="inlineStr">
+      <c r="F188" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13073,7 +13640,10 @@
       <c r="D189" s="4">
         <v>4</v>
       </c>
-      <c r="E189" s="6" t="inlineStr">
+      <c r="E189" s="4">
+        <v>4</v>
+      </c>
+      <c r="F189" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13143,9 +13713,12 @@
         </is>
       </c>
       <c r="D190" s="4">
-        <v>1</v>
-      </c>
-      <c r="E190" s="6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="E190" s="4">
+        <v>1</v>
+      </c>
+      <c r="F190" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13217,7 +13790,10 @@
       <c r="D191" s="4">
         <v>2</v>
       </c>
-      <c r="E191" s="6" t="inlineStr">
+      <c r="E191" s="4">
+        <v>2</v>
+      </c>
+      <c r="F191" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13287,9 +13863,12 @@
         </is>
       </c>
       <c r="D192" s="4">
-        <v>1</v>
-      </c>
-      <c r="E192" s="6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="E192" s="4">
+        <v>1</v>
+      </c>
+      <c r="F192" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13361,7 +13940,10 @@
       <c r="D193" s="4">
         <v>2</v>
       </c>
-      <c r="E193" s="6" t="inlineStr">
+      <c r="E193" s="4">
+        <v>2</v>
+      </c>
+      <c r="F193" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13431,9 +14013,12 @@
         </is>
       </c>
       <c r="D194" s="4">
-        <v>1</v>
-      </c>
-      <c r="E194" s="6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="E194" s="4">
+        <v>1</v>
+      </c>
+      <c r="F194" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13505,7 +14090,10 @@
       <c r="D195" s="4">
         <v>2</v>
       </c>
-      <c r="E195" s="6" t="inlineStr">
+      <c r="E195" s="4">
+        <v>2</v>
+      </c>
+      <c r="F195" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13559,112 +14147,147 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="105">
+  <mergeCells count="140">
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B2:B4"/>
     <mergeCell ref="C2:C4"/>
+    <mergeCell ref="D2:D4"/>
     <mergeCell ref="A6:A10"/>
     <mergeCell ref="B6:B10"/>
     <mergeCell ref="C6:C10"/>
+    <mergeCell ref="D6:D10"/>
     <mergeCell ref="A11:A12"/>
     <mergeCell ref="B11:B12"/>
     <mergeCell ref="C11:C12"/>
+    <mergeCell ref="D11:D12"/>
     <mergeCell ref="A13:A14"/>
     <mergeCell ref="B13:B14"/>
     <mergeCell ref="C13:C14"/>
+    <mergeCell ref="D13:D14"/>
     <mergeCell ref="A26:A30"/>
     <mergeCell ref="B26:B30"/>
     <mergeCell ref="C26:C30"/>
+    <mergeCell ref="D26:D30"/>
     <mergeCell ref="A31:A33"/>
     <mergeCell ref="B31:B33"/>
     <mergeCell ref="C31:C33"/>
+    <mergeCell ref="D31:D33"/>
     <mergeCell ref="A53:A54"/>
     <mergeCell ref="B53:B54"/>
     <mergeCell ref="C53:C54"/>
+    <mergeCell ref="D53:D54"/>
     <mergeCell ref="A60:A61"/>
     <mergeCell ref="B60:B61"/>
     <mergeCell ref="C60:C61"/>
+    <mergeCell ref="D60:D61"/>
     <mergeCell ref="A71:A72"/>
     <mergeCell ref="B71:B72"/>
     <mergeCell ref="C71:C72"/>
+    <mergeCell ref="D71:D72"/>
     <mergeCell ref="A74:A75"/>
     <mergeCell ref="B74:B75"/>
     <mergeCell ref="C74:C75"/>
+    <mergeCell ref="D74:D75"/>
     <mergeCell ref="A76:A77"/>
     <mergeCell ref="B76:B77"/>
     <mergeCell ref="C76:C77"/>
+    <mergeCell ref="D76:D77"/>
     <mergeCell ref="A87:A88"/>
     <mergeCell ref="B87:B88"/>
     <mergeCell ref="C87:C88"/>
+    <mergeCell ref="D87:D88"/>
     <mergeCell ref="A90:A92"/>
     <mergeCell ref="B90:B92"/>
     <mergeCell ref="C90:C92"/>
+    <mergeCell ref="D90:D92"/>
     <mergeCell ref="A94:A95"/>
     <mergeCell ref="B94:B95"/>
     <mergeCell ref="C94:C95"/>
+    <mergeCell ref="D94:D95"/>
     <mergeCell ref="A97:A98"/>
     <mergeCell ref="B97:B98"/>
     <mergeCell ref="C97:C98"/>
+    <mergeCell ref="D97:D98"/>
     <mergeCell ref="A108:A109"/>
     <mergeCell ref="B108:B109"/>
     <mergeCell ref="C108:C109"/>
+    <mergeCell ref="D108:D109"/>
     <mergeCell ref="A117:A118"/>
     <mergeCell ref="B117:B118"/>
     <mergeCell ref="C117:C118"/>
+    <mergeCell ref="D117:D118"/>
     <mergeCell ref="A129:A130"/>
     <mergeCell ref="B129:B130"/>
     <mergeCell ref="C129:C130"/>
+    <mergeCell ref="D129:D130"/>
     <mergeCell ref="A132:A133"/>
     <mergeCell ref="B132:B133"/>
     <mergeCell ref="C132:C133"/>
+    <mergeCell ref="D132:D133"/>
     <mergeCell ref="A137:A139"/>
     <mergeCell ref="B137:B139"/>
     <mergeCell ref="C137:C139"/>
+    <mergeCell ref="D137:D139"/>
     <mergeCell ref="A141:A143"/>
     <mergeCell ref="B141:B143"/>
     <mergeCell ref="C141:C143"/>
+    <mergeCell ref="D141:D143"/>
     <mergeCell ref="A145:A147"/>
     <mergeCell ref="B145:B147"/>
     <mergeCell ref="C145:C147"/>
+    <mergeCell ref="D145:D147"/>
     <mergeCell ref="A149:A150"/>
     <mergeCell ref="B149:B150"/>
     <mergeCell ref="C149:C150"/>
+    <mergeCell ref="D149:D150"/>
     <mergeCell ref="A154:A155"/>
     <mergeCell ref="B154:B155"/>
     <mergeCell ref="C154:C155"/>
+    <mergeCell ref="D154:D155"/>
     <mergeCell ref="A157:A158"/>
     <mergeCell ref="B157:B158"/>
     <mergeCell ref="C157:C158"/>
+    <mergeCell ref="D157:D158"/>
     <mergeCell ref="A160:A162"/>
     <mergeCell ref="B160:B162"/>
     <mergeCell ref="C160:C162"/>
+    <mergeCell ref="D160:D162"/>
     <mergeCell ref="A163:A165"/>
     <mergeCell ref="B163:B165"/>
     <mergeCell ref="C163:C165"/>
+    <mergeCell ref="D163:D165"/>
     <mergeCell ref="A166:A168"/>
     <mergeCell ref="B166:B168"/>
     <mergeCell ref="C166:C168"/>
+    <mergeCell ref="D166:D168"/>
     <mergeCell ref="A169:A170"/>
     <mergeCell ref="B169:B170"/>
     <mergeCell ref="C169:C170"/>
+    <mergeCell ref="D169:D170"/>
     <mergeCell ref="A172:A174"/>
     <mergeCell ref="B172:B174"/>
     <mergeCell ref="C172:C174"/>
+    <mergeCell ref="D172:D174"/>
     <mergeCell ref="A178:A185"/>
     <mergeCell ref="B178:B185"/>
     <mergeCell ref="C178:C185"/>
+    <mergeCell ref="D178:D185"/>
     <mergeCell ref="A186:A189"/>
     <mergeCell ref="B186:B189"/>
     <mergeCell ref="C186:C189"/>
+    <mergeCell ref="D186:D189"/>
     <mergeCell ref="A190:A191"/>
     <mergeCell ref="B190:B191"/>
     <mergeCell ref="C190:C191"/>
+    <mergeCell ref="D190:D191"/>
     <mergeCell ref="A192:A193"/>
     <mergeCell ref="B192:B193"/>
     <mergeCell ref="C192:C193"/>
+    <mergeCell ref="D192:D193"/>
     <mergeCell ref="A194:A195"/>
     <mergeCell ref="B194:B195"/>
     <mergeCell ref="C194:C195"/>
+    <mergeCell ref="D194:D195"/>
   </mergeCells>
   <printOptions gridLines="1" gridLinesSet="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
